--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I236"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8222,6 +8222,39 @@
         <v>368.88</v>
       </c>
       <c r="I236" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="C237" t="n">
+        <v>374.09</v>
+      </c>
+      <c r="D237" t="n">
+        <v>375.53</v>
+      </c>
+      <c r="E237" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="F237" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="G237" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="H237" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="I237" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8238,7 +8271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B241"/>
+  <dimension ref="A1:B242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +10684,16 @@
       </c>
       <c r="B241" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -10819,28 +10862,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07251781957634214</v>
+        <v>0.06989944927426667</v>
       </c>
       <c r="J2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007397040531143872</v>
+        <v>0.006938880761791499</v>
       </c>
       <c r="M2" t="n">
-        <v>5.080297001794191</v>
+        <v>5.069760999586949</v>
       </c>
       <c r="N2" t="n">
-        <v>41.84681263365407</v>
+        <v>41.70972838738889</v>
       </c>
       <c r="O2" t="n">
-        <v>6.468911240205268</v>
+        <v>6.458306928862153</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7064713272595</v>
+        <v>372.7306420368139</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10901,28 +10944,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06893329862577563</v>
+        <v>0.06692247888720362</v>
       </c>
       <c r="J3" t="n">
+        <v>236</v>
+      </c>
+      <c r="K3" t="n">
         <v>235</v>
       </c>
-      <c r="K3" t="n">
-        <v>234</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.008816028904441331</v>
+        <v>0.00839093908370514</v>
       </c>
       <c r="M3" t="n">
-        <v>4.297200791055602</v>
+        <v>4.288781826324722</v>
       </c>
       <c r="N3" t="n">
-        <v>31.59077351188599</v>
+        <v>31.48000571084745</v>
       </c>
       <c r="O3" t="n">
-        <v>5.620567009820806</v>
+        <v>5.610704564566508</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6649302713208</v>
+        <v>374.6835705839231</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10979,28 +11022,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1137145539674116</v>
+        <v>0.1097178656331628</v>
       </c>
       <c r="J4" t="n">
+        <v>236</v>
+      </c>
+      <c r="K4" t="n">
         <v>235</v>
       </c>
-      <c r="K4" t="n">
-        <v>234</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01713225107856664</v>
+        <v>0.01609382319633901</v>
       </c>
       <c r="M4" t="n">
-        <v>5.368917502484313</v>
+        <v>5.365916732083378</v>
       </c>
       <c r="N4" t="n">
-        <v>43.86656536419597</v>
+        <v>43.773372475515</v>
       </c>
       <c r="O4" t="n">
-        <v>6.623183929515771</v>
+        <v>6.616144834835088</v>
       </c>
       <c r="P4" t="n">
-        <v>377.2814839228715</v>
+        <v>377.3185332508124</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11057,28 +11100,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02670618938111793</v>
+        <v>0.02196756320692668</v>
       </c>
       <c r="J5" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K5" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001038414680761934</v>
+        <v>0.0007076791086889633</v>
       </c>
       <c r="M5" t="n">
-        <v>4.90022415753925</v>
+        <v>4.900697981221701</v>
       </c>
       <c r="N5" t="n">
-        <v>40.68713963383862</v>
+        <v>40.64650832237059</v>
       </c>
       <c r="O5" t="n">
-        <v>6.378647163297138</v>
+        <v>6.375461420349949</v>
       </c>
       <c r="P5" t="n">
-        <v>379.4478088052663</v>
+        <v>379.4915520286189</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11135,28 +11178,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08519980058909969</v>
+        <v>0.08025614135230563</v>
       </c>
       <c r="J6" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K6" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008351629421862072</v>
+        <v>0.007471467102399654</v>
       </c>
       <c r="M6" t="n">
-        <v>5.379245916315321</v>
+        <v>5.376670290756798</v>
       </c>
       <c r="N6" t="n">
-        <v>51.11154225939848</v>
+        <v>51.03838957624036</v>
       </c>
       <c r="O6" t="n">
-        <v>7.149233683367643</v>
+        <v>7.144115730882329</v>
       </c>
       <c r="P6" t="n">
-        <v>373.4235073520095</v>
+        <v>373.4691432773229</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11213,28 +11256,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06082149723777287</v>
+        <v>0.0571767229374096</v>
       </c>
       <c r="J7" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K7" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006670512813352514</v>
+        <v>0.005945017160014832</v>
       </c>
       <c r="M7" t="n">
-        <v>4.322953008920105</v>
+        <v>4.320092147901824</v>
       </c>
       <c r="N7" t="n">
-        <v>32.66657941721716</v>
+        <v>32.60611939304108</v>
       </c>
       <c r="O7" t="n">
-        <v>5.715468433752141</v>
+        <v>5.710176826775252</v>
       </c>
       <c r="P7" t="n">
-        <v>373.8087065151133</v>
+        <v>373.8423521690285</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11291,28 +11334,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1380535366745941</v>
+        <v>0.1322100703350487</v>
       </c>
       <c r="J8" t="n">
+        <v>236</v>
+      </c>
+      <c r="K8" t="n">
         <v>235</v>
       </c>
-      <c r="K8" t="n">
-        <v>234</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0382887948985805</v>
+        <v>0.03533214199178514</v>
       </c>
       <c r="M8" t="n">
-        <v>4.001212755108703</v>
+        <v>4.008701548510765</v>
       </c>
       <c r="N8" t="n">
-        <v>28.25562925881383</v>
+        <v>28.33465895008342</v>
       </c>
       <c r="O8" t="n">
-        <v>5.315602436113316</v>
+        <v>5.323030992778778</v>
       </c>
       <c r="P8" t="n">
-        <v>372.8384605634846</v>
+        <v>372.8926991580905</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11350,7 +11393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I236"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22433,6 +22476,53 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-34.81007026173398,173.1634209094665</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>-34.81079630660915,173.16356960389308</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>-34.8115147238286,173.16373760076374</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-34.81222042630835,173.16394658372735</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-34.81291882706998,173.16421770036453</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-34.8135980103962,173.1645647825629</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-34.81428090908464,173.16490047083107</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8255,6 +8255,39 @@
         <v>369.55</v>
       </c>
       <c r="I237" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="C238" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="D238" t="n">
+        <v>376.97</v>
+      </c>
+      <c r="E238" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="F238" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="G238" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="H238" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="I238" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8271,7 +8304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10694,6 +10727,16 @@
       </c>
       <c r="B242" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -10862,28 +10905,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06989944927426667</v>
+        <v>0.06793100851306416</v>
       </c>
       <c r="J2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006938880761791499</v>
+        <v>0.006617896055408523</v>
       </c>
       <c r="M2" t="n">
-        <v>5.069760999586949</v>
+        <v>5.056732151342917</v>
       </c>
       <c r="N2" t="n">
-        <v>41.70972838738889</v>
+        <v>41.55686628939167</v>
       </c>
       <c r="O2" t="n">
-        <v>6.458306928862153</v>
+        <v>6.446461532452642</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7306420368139</v>
+        <v>372.7488494466076</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10944,28 +10987,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06692247888720362</v>
+        <v>0.06641268470570558</v>
       </c>
       <c r="J3" t="n">
+        <v>237</v>
+      </c>
+      <c r="K3" t="n">
         <v>236</v>
       </c>
-      <c r="K3" t="n">
-        <v>235</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00839093908370514</v>
+        <v>0.008346602840205164</v>
       </c>
       <c r="M3" t="n">
-        <v>4.288781826324722</v>
+        <v>4.273111949224441</v>
       </c>
       <c r="N3" t="n">
-        <v>31.48000571084745</v>
+        <v>31.34816272965223</v>
       </c>
       <c r="O3" t="n">
-        <v>5.610704564566508</v>
+        <v>5.59894300110764</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6835705839231</v>
+        <v>374.688305829237</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11022,28 +11065,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1097178656331628</v>
+        <v>0.107021922919866</v>
       </c>
       <c r="J4" t="n">
+        <v>237</v>
+      </c>
+      <c r="K4" t="n">
         <v>236</v>
       </c>
-      <c r="K4" t="n">
-        <v>235</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01609382319633901</v>
+        <v>0.01546114115117447</v>
       </c>
       <c r="M4" t="n">
-        <v>5.365916732083378</v>
+        <v>5.35647602943318</v>
       </c>
       <c r="N4" t="n">
-        <v>43.773372475515</v>
+        <v>43.63115206952679</v>
       </c>
       <c r="O4" t="n">
-        <v>6.616144834835088</v>
+        <v>6.605388108924925</v>
       </c>
       <c r="P4" t="n">
-        <v>377.3185332508124</v>
+        <v>377.3435746313599</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11100,28 +11143,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02196756320692668</v>
+        <v>0.01810252052332766</v>
       </c>
       <c r="J5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007076791086889633</v>
+        <v>0.0004844347859992437</v>
       </c>
       <c r="M5" t="n">
-        <v>4.900697981221701</v>
+        <v>4.897200486861855</v>
       </c>
       <c r="N5" t="n">
-        <v>40.64650832237059</v>
+        <v>40.56417184155507</v>
       </c>
       <c r="O5" t="n">
-        <v>6.375461420349949</v>
+        <v>6.369000851119042</v>
       </c>
       <c r="P5" t="n">
-        <v>379.4915520286189</v>
+        <v>379.5273023632987</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11178,28 +11221,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08025614135230563</v>
+        <v>0.07572426822423271</v>
       </c>
       <c r="J6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007471467102399654</v>
+        <v>0.006707346657723434</v>
       </c>
       <c r="M6" t="n">
-        <v>5.376670290756798</v>
+        <v>5.372923151231642</v>
       </c>
       <c r="N6" t="n">
-        <v>51.03838957624036</v>
+        <v>50.94562765821786</v>
       </c>
       <c r="O6" t="n">
-        <v>7.144115730882329</v>
+        <v>7.137620587998346</v>
       </c>
       <c r="P6" t="n">
-        <v>373.4691432773229</v>
+        <v>373.5110615675768</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11256,28 +11299,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0571767229374096</v>
+        <v>0.05328281114866742</v>
       </c>
       <c r="J7" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K7" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005945017160014832</v>
+        <v>0.005204114578428065</v>
       </c>
       <c r="M7" t="n">
-        <v>4.320092147901824</v>
+        <v>4.318679782023702</v>
       </c>
       <c r="N7" t="n">
-        <v>32.60611939304108</v>
+        <v>32.55904561762021</v>
       </c>
       <c r="O7" t="n">
-        <v>5.710176826775252</v>
+        <v>5.706053418749268</v>
       </c>
       <c r="P7" t="n">
-        <v>373.8423521690285</v>
+        <v>373.878369533145</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11334,28 +11377,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1322100703350487</v>
+        <v>0.1269960069703193</v>
       </c>
       <c r="J8" t="n">
+        <v>237</v>
+      </c>
+      <c r="K8" t="n">
         <v>236</v>
       </c>
-      <c r="K8" t="n">
-        <v>235</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03533214199178514</v>
+        <v>0.03282601910083582</v>
       </c>
       <c r="M8" t="n">
-        <v>4.008701548510765</v>
+        <v>4.014117081559258</v>
       </c>
       <c r="N8" t="n">
-        <v>28.33465895008342</v>
+        <v>28.37596964145332</v>
       </c>
       <c r="O8" t="n">
-        <v>5.323030992778778</v>
+        <v>5.326909952444598</v>
       </c>
       <c r="P8" t="n">
-        <v>372.8926991580905</v>
+        <v>372.9411922428681</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11393,7 +11436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22523,6 +22566,53 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>-34.81006940704593,173.16342849241803</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>-34.81079389557764,173.16358840236555</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>-34.81151199180389,173.16375299283513</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-34.81221793044798,173.1639560620786</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-34.81291767313621,173.16422126227246</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-34.81359942387242,173.16456064018647</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-34.81427882416725,173.1649064059555</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8288,6 +8288,72 @@
         <v>370.14</v>
       </c>
       <c r="I238" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="C239" t="n">
+        <v>372.79</v>
+      </c>
+      <c r="D239" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="E239" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="F239" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="G239" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="H239" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="C240" t="n">
+        <v>374.06</v>
+      </c>
+      <c r="D240" t="n">
+        <v>374.74</v>
+      </c>
+      <c r="E240" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="F240" t="n">
+        <v>369.11</v>
+      </c>
+      <c r="G240" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="H240" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="I240" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8304,7 +8370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B243"/>
+  <dimension ref="A1:B245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10737,6 +10803,26 @@
       </c>
       <c r="B243" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -10905,28 +10991,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06793100851306416</v>
+        <v>0.05979617250308498</v>
       </c>
       <c r="J2" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K2" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006617896055408523</v>
+        <v>0.005211333365386372</v>
       </c>
       <c r="M2" t="n">
-        <v>5.056732151342917</v>
+        <v>5.049863394382657</v>
       </c>
       <c r="N2" t="n">
-        <v>41.55686628939167</v>
+        <v>41.41426883642293</v>
       </c>
       <c r="O2" t="n">
-        <v>6.446461532452642</v>
+        <v>6.435391894548686</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7488494466076</v>
+        <v>372.8243528268349</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10987,28 +11073,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06641268470570558</v>
+        <v>0.06147934459891258</v>
       </c>
       <c r="J3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K3" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008346602840205164</v>
+        <v>0.007284698595090289</v>
       </c>
       <c r="M3" t="n">
-        <v>4.273111949224441</v>
+        <v>4.261513948284578</v>
       </c>
       <c r="N3" t="n">
-        <v>31.34816272965223</v>
+        <v>31.16209546617718</v>
       </c>
       <c r="O3" t="n">
-        <v>5.59894300110764</v>
+        <v>5.582301986293573</v>
       </c>
       <c r="P3" t="n">
-        <v>374.688305829237</v>
+        <v>374.7342851273304</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11065,28 +11151,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.107021922919866</v>
+        <v>0.09769009115141522</v>
       </c>
       <c r="J4" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01546114115117447</v>
+        <v>0.0130901994145094</v>
       </c>
       <c r="M4" t="n">
-        <v>5.35647602943318</v>
+        <v>5.356789014761437</v>
       </c>
       <c r="N4" t="n">
-        <v>43.63115206952679</v>
+        <v>43.52986256375412</v>
       </c>
       <c r="O4" t="n">
-        <v>6.605388108924925</v>
+        <v>6.597716465850447</v>
       </c>
       <c r="P4" t="n">
-        <v>377.3435746313599</v>
+        <v>377.4305555170891</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11143,28 +11229,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01810252052332766</v>
+        <v>0.008965456469205779</v>
       </c>
       <c r="J5" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K5" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004844347859992437</v>
+        <v>0.0001204632192245425</v>
       </c>
       <c r="M5" t="n">
-        <v>4.897200486861855</v>
+        <v>4.897052505595516</v>
       </c>
       <c r="N5" t="n">
-        <v>40.56417184155507</v>
+        <v>40.48175020847615</v>
       </c>
       <c r="O5" t="n">
-        <v>6.369000851119042</v>
+        <v>6.362527030078234</v>
       </c>
       <c r="P5" t="n">
-        <v>379.5273023632987</v>
+        <v>379.6121092140089</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11221,28 +11307,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07572426822423271</v>
+        <v>0.06485191389090519</v>
       </c>
       <c r="J6" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K6" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006707346657723434</v>
+        <v>0.004990513734985824</v>
       </c>
       <c r="M6" t="n">
-        <v>5.372923151231642</v>
+        <v>5.374995862900637</v>
       </c>
       <c r="N6" t="n">
-        <v>50.94562765821786</v>
+        <v>50.88020046442568</v>
       </c>
       <c r="O6" t="n">
-        <v>7.137620587998346</v>
+        <v>7.133035851895438</v>
       </c>
       <c r="P6" t="n">
-        <v>373.5110615675768</v>
+        <v>373.6119777693985</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11299,28 +11385,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05328281114866742</v>
+        <v>0.04015608247152138</v>
       </c>
       <c r="J7" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K7" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005204114578428065</v>
+        <v>0.002972946144212396</v>
       </c>
       <c r="M7" t="n">
-        <v>4.318679782023702</v>
+        <v>4.3389187724337</v>
       </c>
       <c r="N7" t="n">
-        <v>32.55904561762021</v>
+        <v>32.81284060531017</v>
       </c>
       <c r="O7" t="n">
-        <v>5.706053418749268</v>
+        <v>5.728249349086523</v>
       </c>
       <c r="P7" t="n">
-        <v>373.878369533145</v>
+        <v>374.0002158623737</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11377,28 +11463,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1269960069703193</v>
+        <v>0.1126848633810907</v>
       </c>
       <c r="J8" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K8" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03282601910083582</v>
+        <v>0.02597316906551905</v>
       </c>
       <c r="M8" t="n">
-        <v>4.014117081559258</v>
+        <v>4.04292452146889</v>
       </c>
       <c r="N8" t="n">
-        <v>28.37596964145332</v>
+        <v>28.75838824728169</v>
       </c>
       <c r="O8" t="n">
-        <v>5.326909952444598</v>
+        <v>5.362684798427154</v>
       </c>
       <c r="P8" t="n">
-        <v>372.9411922428681</v>
+        <v>373.074758733661</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11436,7 +11522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22613,6 +22699,100 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-34.81007342407572,173.16339285254452</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>-34.810798107952635,173.1635555590566</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-34.81151728510002,173.16372317069593</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-34.81222226391935,173.16393960516066</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-34.81292281638306,173.16420538633915</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-34.813610007702096,173.1645296228754</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-34.81428755254828,173.16488155890718</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-34.81007186122038,173.16340671851395</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>-34.810796348178634,173.16356927978146</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-34.811516222646894,173.16372915650194</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-34.812219246945844,173.16395106250877</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-34.81292106899815,173.16421078008594</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-34.81361248990204,173.16452234845602</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-34.81428832997469,173.16487934580948</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I240"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8354,6 +8354,39 @@
         <v>367.45</v>
       </c>
       <c r="I240" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="C241" t="n">
+        <v>375.41</v>
+      </c>
+      <c r="D241" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="E241" t="n">
+        <v>376.01</v>
+      </c>
+      <c r="F241" t="n">
+        <v>369.32</v>
+      </c>
+      <c r="G241" t="n">
+        <v>366.59</v>
+      </c>
+      <c r="H241" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="I241" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8370,7 +8403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B245"/>
+  <dimension ref="A1:B246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10823,6 +10856,16 @@
       </c>
       <c r="B245" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -10991,28 +11034,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05979617250308498</v>
+        <v>0.05764357634629498</v>
       </c>
       <c r="J2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005211333365386372</v>
+        <v>0.004888130275811919</v>
       </c>
       <c r="M2" t="n">
-        <v>5.049863394382657</v>
+        <v>5.038149709253315</v>
       </c>
       <c r="N2" t="n">
-        <v>41.41426883642293</v>
+        <v>41.27077511788203</v>
       </c>
       <c r="O2" t="n">
-        <v>6.435391894548686</v>
+        <v>6.424233426478371</v>
       </c>
       <c r="P2" t="n">
-        <v>372.8243528268349</v>
+        <v>372.844384154334</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11073,28 +11116,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06147934459891258</v>
+        <v>0.06071641323894527</v>
       </c>
       <c r="J3" t="n">
+        <v>240</v>
+      </c>
+      <c r="K3" t="n">
         <v>239</v>
       </c>
-      <c r="K3" t="n">
-        <v>238</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.007284698595090289</v>
+        <v>0.007174080852408893</v>
       </c>
       <c r="M3" t="n">
-        <v>4.261513948284578</v>
+        <v>4.24743997751297</v>
       </c>
       <c r="N3" t="n">
-        <v>31.16209546617718</v>
+        <v>31.03535079251583</v>
       </c>
       <c r="O3" t="n">
-        <v>5.582301986293573</v>
+        <v>5.570938053193181</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7342851273304</v>
+        <v>374.7414145537924</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11151,28 +11194,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09769009115141522</v>
+        <v>0.0940699510638663</v>
       </c>
       <c r="J4" t="n">
+        <v>240</v>
+      </c>
+      <c r="K4" t="n">
         <v>239</v>
       </c>
-      <c r="K4" t="n">
-        <v>238</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0130901994145094</v>
+        <v>0.01224341416580033</v>
       </c>
       <c r="M4" t="n">
-        <v>5.356789014761437</v>
+        <v>5.35179632791824</v>
       </c>
       <c r="N4" t="n">
-        <v>43.52986256375412</v>
+        <v>43.42970026054116</v>
       </c>
       <c r="O4" t="n">
-        <v>6.597716465850447</v>
+        <v>6.590121414704069</v>
       </c>
       <c r="P4" t="n">
-        <v>377.4305555170891</v>
+        <v>377.4643849333256</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11229,28 +11272,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008965456469205779</v>
+        <v>0.00585546312599314</v>
       </c>
       <c r="J5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001204632192245425</v>
+        <v>5.180988214337212e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.897052505595516</v>
+        <v>4.891340753527729</v>
       </c>
       <c r="N5" t="n">
-        <v>40.48175020847615</v>
+        <v>40.37374640456898</v>
       </c>
       <c r="O5" t="n">
-        <v>6.362527030078234</v>
+        <v>6.354033868698607</v>
       </c>
       <c r="P5" t="n">
-        <v>379.6121092140089</v>
+        <v>379.6410497540081</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11307,28 +11350,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06485191389090519</v>
+        <v>0.05999365718966235</v>
       </c>
       <c r="J6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004990513734985824</v>
+        <v>0.004302758772048665</v>
       </c>
       <c r="M6" t="n">
-        <v>5.374995862900637</v>
+        <v>5.374018447645226</v>
       </c>
       <c r="N6" t="n">
-        <v>50.88020046442568</v>
+        <v>50.81625259252778</v>
       </c>
       <c r="O6" t="n">
-        <v>7.133035851895438</v>
+        <v>7.128551928163796</v>
       </c>
       <c r="P6" t="n">
-        <v>373.6119777693985</v>
+        <v>373.6571870534301</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11385,28 +11428,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04015608247152138</v>
+        <v>0.03330695448472199</v>
       </c>
       <c r="J7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002972946144212396</v>
+        <v>0.002048646169841906</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3389187724337</v>
+        <v>4.350242003230276</v>
       </c>
       <c r="N7" t="n">
-        <v>32.81284060531017</v>
+        <v>32.97037740108246</v>
       </c>
       <c r="O7" t="n">
-        <v>5.728249349086523</v>
+        <v>5.741983751377433</v>
       </c>
       <c r="P7" t="n">
-        <v>374.0002158623737</v>
+        <v>374.0639515172732</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11463,28 +11506,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1126848633810907</v>
+        <v>0.1056332467308796</v>
       </c>
       <c r="J8" t="n">
+        <v>240</v>
+      </c>
+      <c r="K8" t="n">
         <v>239</v>
       </c>
-      <c r="K8" t="n">
-        <v>238</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.02597316906551905</v>
+        <v>0.02287200860176541</v>
       </c>
       <c r="M8" t="n">
-        <v>4.04292452146889</v>
+        <v>4.057006754885293</v>
       </c>
       <c r="N8" t="n">
-        <v>28.75838824728169</v>
+        <v>28.94824438237444</v>
       </c>
       <c r="O8" t="n">
-        <v>5.362684798427154</v>
+        <v>5.380357272744481</v>
       </c>
       <c r="P8" t="n">
-        <v>373.074758733661</v>
+        <v>373.1407380689905</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11522,7 +11565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I240"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22793,6 +22836,53 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-34.81006996869813,173.16342350933564</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>-34.810794477551035,173.16358386480334</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-34.811514704856215,173.16373770765313</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-34.812216367106494,173.16396199906754</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-34.81292037663802,173.16421291723086</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-34.81361348967691,173.1645194184814</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-34.814288612675185,173.1648785410467</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I241"/>
+  <dimension ref="A1:I243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8389,6 +8389,72 @@
       <c r="I241" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>373.56</v>
+      </c>
+      <c r="C242" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="D242" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="E242" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="F242" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="G242" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="H242" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>372.07</v>
+      </c>
+      <c r="C243" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="D243" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="E243" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="F243" t="n">
+        <v>369.11</v>
+      </c>
+      <c r="G243" t="n">
+        <v>366.09</v>
+      </c>
+      <c r="H243" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B246"/>
+  <dimension ref="A1:B248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10866,6 +10932,26 @@
       </c>
       <c r="B246" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -11034,28 +11120,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05764357634629498</v>
+        <v>0.05514580490223156</v>
       </c>
       <c r="J2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004888130275811919</v>
+        <v>0.004560642647204571</v>
       </c>
       <c r="M2" t="n">
-        <v>5.038149709253315</v>
+        <v>5.007103681810789</v>
       </c>
       <c r="N2" t="n">
-        <v>41.27077511788203</v>
+        <v>40.95378368183682</v>
       </c>
       <c r="O2" t="n">
-        <v>6.424233426478371</v>
+        <v>6.39951433171587</v>
       </c>
       <c r="P2" t="n">
-        <v>372.844384154334</v>
+        <v>372.8678663600919</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11116,28 +11202,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06071641323894527</v>
+        <v>0.06161301086202951</v>
       </c>
       <c r="J3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007174080852408893</v>
+        <v>0.007529747907129458</v>
       </c>
       <c r="M3" t="n">
-        <v>4.24743997751297</v>
+        <v>4.216886423821846</v>
       </c>
       <c r="N3" t="n">
-        <v>31.03535079251583</v>
+        <v>30.78032814569552</v>
       </c>
       <c r="O3" t="n">
-        <v>5.570938053193181</v>
+        <v>5.548002176071628</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7414145537924</v>
+        <v>374.7329548621597</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11194,28 +11280,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0940699510638663</v>
+        <v>0.084474606384255</v>
       </c>
       <c r="J4" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K4" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01224341416580033</v>
+        <v>0.01002304945650734</v>
       </c>
       <c r="M4" t="n">
-        <v>5.35179632791824</v>
+        <v>5.352620462721243</v>
       </c>
       <c r="N4" t="n">
-        <v>43.42970026054116</v>
+        <v>43.35796424632206</v>
       </c>
       <c r="O4" t="n">
-        <v>6.590121414704069</v>
+        <v>6.584676472410931</v>
       </c>
       <c r="P4" t="n">
-        <v>377.4643849333256</v>
+        <v>377.554916190649</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11272,28 +11358,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00585546312599314</v>
+        <v>-0.0007853732979317864</v>
       </c>
       <c r="J5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L5" t="n">
-        <v>5.180988214337212e-05</v>
+        <v>9.471991319065509e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>4.891340753527729</v>
+        <v>4.881570085258401</v>
       </c>
       <c r="N5" t="n">
-        <v>40.37374640456898</v>
+        <v>40.1782363029683</v>
       </c>
       <c r="O5" t="n">
-        <v>6.354033868698607</v>
+        <v>6.338630475344678</v>
       </c>
       <c r="P5" t="n">
-        <v>379.6410497540081</v>
+        <v>379.7034388358534</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11350,28 +11436,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05999365718966235</v>
+        <v>0.05130415970420041</v>
       </c>
       <c r="J6" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K6" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004302758772048665</v>
+        <v>0.003196896096500645</v>
       </c>
       <c r="M6" t="n">
-        <v>5.374018447645226</v>
+        <v>5.367115643009639</v>
       </c>
       <c r="N6" t="n">
-        <v>50.81625259252778</v>
+        <v>50.63680859307268</v>
       </c>
       <c r="O6" t="n">
-        <v>7.128551928163796</v>
+        <v>7.115954510329074</v>
       </c>
       <c r="P6" t="n">
-        <v>373.6571870534301</v>
+        <v>373.73883659147</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11428,28 +11514,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03330695448472199</v>
+        <v>0.02031712634832429</v>
       </c>
       <c r="J7" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K7" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002048646169841906</v>
+        <v>0.0007658298850906631</v>
       </c>
       <c r="M7" t="n">
-        <v>4.350242003230276</v>
+        <v>4.36924771748009</v>
       </c>
       <c r="N7" t="n">
-        <v>32.97037740108246</v>
+        <v>33.2307266582275</v>
       </c>
       <c r="O7" t="n">
-        <v>5.741983751377433</v>
+        <v>5.764609844406428</v>
       </c>
       <c r="P7" t="n">
-        <v>374.0639515172732</v>
+        <v>374.1860012324353</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11506,28 +11592,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1056332467308796</v>
+        <v>0.09286466596643797</v>
       </c>
       <c r="J8" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K8" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02287200860176541</v>
+        <v>0.01780084383225589</v>
       </c>
       <c r="M8" t="n">
-        <v>4.057006754885293</v>
+        <v>4.078879499022832</v>
       </c>
       <c r="N8" t="n">
-        <v>28.94824438237444</v>
+        <v>29.22101907855123</v>
       </c>
       <c r="O8" t="n">
-        <v>5.380357272744481</v>
+        <v>5.405646962071351</v>
       </c>
       <c r="P8" t="n">
-        <v>373.1407380689905</v>
+        <v>373.2613654780202</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11565,7 +11651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I241"/>
+  <dimension ref="A1:I243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22883,6 +22969,100 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>-34.810067746507755,173.16344322500913</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>-34.81079248221298,173.16359942215925</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-34.8115169056525,173.1637253084838</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-34.81221713506374,173.16395908265196</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-34.812916354354634,173.16422533302432</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-34.8136100421771,173.16452952184179</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-34.81428345339022,173.16489322796696</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>-34.81006956577375,173.16342708415561</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>-34.81079232979125,173.16360061056832</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-34.81151838549758,173.16371697111092</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-34.81221757389644,173.16395741612874</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-34.81292106899815,173.16421078008594</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-34.813615213426495,173.16451436680092</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-34.81428921341374,173.16487683092572</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I243"/>
+  <dimension ref="A1:I245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8455,6 +8455,72 @@
       <c r="I243" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="C244" t="n">
+        <v>375.91</v>
+      </c>
+      <c r="D244" t="n">
+        <v>372.66</v>
+      </c>
+      <c r="E244" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="F244" t="n">
+        <v>368.22</v>
+      </c>
+      <c r="G244" t="n">
+        <v>365.15</v>
+      </c>
+      <c r="H244" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>370</v>
+      </c>
+      <c r="C245" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="D245" t="n">
+        <v>372.21</v>
+      </c>
+      <c r="E245" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="F245" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="G245" t="n">
+        <v>364.35</v>
+      </c>
+      <c r="H245" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10952,6 +11018,26 @@
       </c>
       <c r="B248" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -11120,28 +11206,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05514580490223156</v>
+        <v>0.04890188879374539</v>
       </c>
       <c r="J2" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004560642647204571</v>
+        <v>0.003647295139896922</v>
       </c>
       <c r="M2" t="n">
-        <v>5.007103681810789</v>
+        <v>4.992168553658111</v>
       </c>
       <c r="N2" t="n">
-        <v>40.95378368183682</v>
+        <v>40.74544779214592</v>
       </c>
       <c r="O2" t="n">
-        <v>6.39951433171587</v>
+        <v>6.383216101006288</v>
       </c>
       <c r="P2" t="n">
-        <v>372.8678663600919</v>
+        <v>372.9267352542096</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11202,28 +11288,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06161301086202951</v>
+        <v>0.06076937221895601</v>
       </c>
       <c r="J3" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007529747907129458</v>
+        <v>0.007465849947061787</v>
       </c>
       <c r="M3" t="n">
-        <v>4.216886423821846</v>
+        <v>4.186408328714705</v>
       </c>
       <c r="N3" t="n">
-        <v>30.78032814569552</v>
+        <v>30.52934324258385</v>
       </c>
       <c r="O3" t="n">
-        <v>5.548002176071628</v>
+        <v>5.525336482295341</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7329548621597</v>
+        <v>374.7409427761011</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11280,28 +11366,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.084474606384255</v>
+        <v>0.07287392125162641</v>
       </c>
       <c r="J4" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01002304945650734</v>
+        <v>0.007545433434962057</v>
       </c>
       <c r="M4" t="n">
-        <v>5.352620462721243</v>
+        <v>5.363594561582211</v>
       </c>
       <c r="N4" t="n">
-        <v>43.35796424632206</v>
+        <v>43.43626566575372</v>
       </c>
       <c r="O4" t="n">
-        <v>6.584676472410931</v>
+        <v>6.590619520633377</v>
       </c>
       <c r="P4" t="n">
-        <v>377.554916190649</v>
+        <v>377.6647429065004</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11358,28 +11444,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0007853732979317864</v>
+        <v>-0.00830033089542433</v>
       </c>
       <c r="J5" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K5" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L5" t="n">
-        <v>9.471991319065509e-07</v>
+        <v>0.0001073302834625478</v>
       </c>
       <c r="M5" t="n">
-        <v>4.881570085258401</v>
+        <v>4.875822894066502</v>
       </c>
       <c r="N5" t="n">
-        <v>40.1782363029683</v>
+        <v>40.03202430373231</v>
       </c>
       <c r="O5" t="n">
-        <v>6.338630475344678</v>
+        <v>6.327086557313113</v>
       </c>
       <c r="P5" t="n">
-        <v>379.7034388358534</v>
+        <v>379.7742867695521</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11436,28 +11522,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05130415970420041</v>
+        <v>0.04037781698093855</v>
       </c>
       <c r="J6" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K6" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003196896096500645</v>
+        <v>0.002005278772092778</v>
       </c>
       <c r="M6" t="n">
-        <v>5.367115643009639</v>
+        <v>5.370906446267854</v>
       </c>
       <c r="N6" t="n">
-        <v>50.63680859307268</v>
+        <v>50.60865431784966</v>
       </c>
       <c r="O6" t="n">
-        <v>7.115954510329074</v>
+        <v>7.113975985189271</v>
       </c>
       <c r="P6" t="n">
-        <v>373.73883659147</v>
+        <v>373.8418441392324</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11514,28 +11600,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02031712634832429</v>
+        <v>0.004668379943817127</v>
       </c>
       <c r="J7" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K7" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007658298850906631</v>
+        <v>4.027053741817443e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.36924771748009</v>
+        <v>4.40177183872698</v>
       </c>
       <c r="N7" t="n">
-        <v>33.2307266582275</v>
+        <v>33.75305644016276</v>
       </c>
       <c r="O7" t="n">
-        <v>5.764609844406428</v>
+        <v>5.809738069841252</v>
       </c>
       <c r="P7" t="n">
-        <v>374.1860012324353</v>
+        <v>374.3335331873344</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11592,28 +11678,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09286466596643797</v>
+        <v>0.07877440963895289</v>
       </c>
       <c r="J8" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K8" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01780084383225589</v>
+        <v>0.01283815876902528</v>
       </c>
       <c r="M8" t="n">
-        <v>4.078879499022832</v>
+        <v>4.109072977399181</v>
       </c>
       <c r="N8" t="n">
-        <v>29.22101907855123</v>
+        <v>29.62029144934884</v>
       </c>
       <c r="O8" t="n">
-        <v>5.405646962071351</v>
+        <v>5.442452705292793</v>
       </c>
       <c r="P8" t="n">
-        <v>373.2613654780202</v>
+        <v>373.3949241331892</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11651,7 +11737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I243"/>
+  <dimension ref="A1:I245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23063,6 +23149,100 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>-34.81007122630995,173.16341235156392</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>-34.81079378472555,173.1635892666631</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-34.811520168899854,173.16370692350733</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-34.81221908238362,173.163951687455</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-34.812924003285886,173.16420172266197</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-34.81361845407516,173.16450486964098</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-34.81429034421563,173.1648736118744</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-34.81007209320681,173.16340466028416</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>-34.810793992573224,173.16358764610519</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-34.81152102265597,173.1637021134842</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-34.81221976805952,173.16394908351234</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-34.81292453079822,173.16420009436092</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-34.813621212073436,173.1644967869511</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-34.814290980291666,173.16487180115803</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0023/nzd0023.xlsx
+++ b/data/nzd0023/nzd0023.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I245"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8521,6 +8521,39 @@
       <c r="I245" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="C246" t="n">
+        <v>374</v>
+      </c>
+      <c r="D246" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="E246" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="F246" t="n">
+        <v>368.61</v>
+      </c>
+      <c r="G246" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="H246" t="n">
+        <v>367.13</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B250"/>
+  <dimension ref="A1:B251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11038,6 +11071,16 @@
       </c>
       <c r="B250" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -11206,28 +11249,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04890188879374539</v>
+        <v>0.04466766328258147</v>
       </c>
       <c r="J2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003647295139896922</v>
+        <v>0.003064653059237865</v>
       </c>
       <c r="M2" t="n">
-        <v>4.992168553658111</v>
+        <v>4.989281282936235</v>
       </c>
       <c r="N2" t="n">
-        <v>40.74544779214592</v>
+        <v>40.69792928124927</v>
       </c>
       <c r="O2" t="n">
-        <v>6.383216101006288</v>
+        <v>6.379492870224817</v>
       </c>
       <c r="P2" t="n">
-        <v>372.9267352542096</v>
+        <v>372.966813881217</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11288,28 +11331,28 @@
         <v>0.0847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06076937221895601</v>
+        <v>0.05892427666105349</v>
       </c>
       <c r="J3" t="n">
+        <v>245</v>
+      </c>
+      <c r="K3" t="n">
         <v>244</v>
       </c>
-      <c r="K3" t="n">
-        <v>243</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.007465849947061787</v>
+        <v>0.007083294093104597</v>
       </c>
       <c r="M3" t="n">
-        <v>4.186408328714705</v>
+        <v>4.178511379803143</v>
       </c>
       <c r="N3" t="n">
-        <v>30.52934324258385</v>
+        <v>30.42671153864369</v>
       </c>
       <c r="O3" t="n">
-        <v>5.525336482295341</v>
+        <v>5.516041292325837</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7409427761011</v>
+        <v>374.7584807518952</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11366,28 +11409,28 @@
         <v>0.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07287392125162641</v>
+        <v>0.06597735286436325</v>
       </c>
       <c r="J4" t="n">
+        <v>245</v>
+      </c>
+      <c r="K4" t="n">
         <v>244</v>
       </c>
-      <c r="K4" t="n">
-        <v>243</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.007545433434962057</v>
+        <v>0.006206731135329879</v>
       </c>
       <c r="M4" t="n">
-        <v>5.363594561582211</v>
+        <v>5.373927016310346</v>
       </c>
       <c r="N4" t="n">
-        <v>43.43626566575372</v>
+        <v>43.57243642190424</v>
       </c>
       <c r="O4" t="n">
-        <v>6.590619520633377</v>
+        <v>6.600942085937752</v>
       </c>
       <c r="P4" t="n">
-        <v>377.6647429065004</v>
+        <v>377.7302960692731</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11444,28 +11487,28 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00830033089542433</v>
+        <v>-0.01247630712592273</v>
       </c>
       <c r="J5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001073302834625478</v>
+        <v>0.0002440496412496884</v>
       </c>
       <c r="M5" t="n">
-        <v>4.875822894066502</v>
+        <v>4.874808928269101</v>
       </c>
       <c r="N5" t="n">
-        <v>40.03202430373231</v>
+        <v>39.98417188741706</v>
       </c>
       <c r="O5" t="n">
-        <v>6.327086557313113</v>
+        <v>6.323303874353743</v>
       </c>
       <c r="P5" t="n">
-        <v>379.7742867695521</v>
+        <v>379.8138140439717</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11522,28 +11565,28 @@
         <v>0.0825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04037781698093855</v>
+        <v>0.03545710896508372</v>
       </c>
       <c r="J6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002005278772092778</v>
+        <v>0.001556687824532776</v>
       </c>
       <c r="M6" t="n">
-        <v>5.370906446267854</v>
+        <v>5.370802342465024</v>
       </c>
       <c r="N6" t="n">
-        <v>50.60865431784966</v>
+        <v>50.56251818657191</v>
       </c>
       <c r="O6" t="n">
-        <v>7.113975985189271</v>
+        <v>7.110732605475466</v>
       </c>
       <c r="P6" t="n">
-        <v>373.8418441392324</v>
+        <v>373.8884205959328</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -11600,28 +11643,28 @@
         <v>0.1304</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004668379943817127</v>
+        <v>-0.003071487540003169</v>
       </c>
       <c r="J7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L7" t="n">
-        <v>4.027053741817443e-05</v>
+        <v>1.739223373431464e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.40177183872698</v>
+        <v>4.41937357104372</v>
       </c>
       <c r="N7" t="n">
-        <v>33.75305644016276</v>
+        <v>34.01220331610654</v>
       </c>
       <c r="O7" t="n">
-        <v>5.809738069841252</v>
+        <v>5.831998226689248</v>
       </c>
       <c r="P7" t="n">
-        <v>374.3335331873344</v>
+        <v>374.4067941086418</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -11678,28 +11721,28 @@
         <v>0.0828</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07877440963895289</v>
+        <v>0.07221692570725123</v>
       </c>
       <c r="J8" t="n">
+        <v>245</v>
+      </c>
+      <c r="K8" t="n">
         <v>244</v>
       </c>
-      <c r="K8" t="n">
-        <v>243</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01283815876902528</v>
+        <v>0.01081047952426495</v>
       </c>
       <c r="M8" t="n">
-        <v>4.109072977399181</v>
+        <v>4.12280774989591</v>
       </c>
       <c r="N8" t="n">
-        <v>29.62029144934884</v>
+        <v>29.78220436678765</v>
       </c>
       <c r="O8" t="n">
-        <v>5.442452705292793</v>
+        <v>5.457307428282527</v>
       </c>
       <c r="P8" t="n">
-        <v>373.3949241331892</v>
+        <v>373.4573309362211</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -11737,7 +11780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I245"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23243,6 +23286,53 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-34.810073558383515,173.16339166093775</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-34.810796431317605,173.16356863155826</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-34.81152371672958,173.16368693518828</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-34.81222133140038,173.1639431465229</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-34.812922717474486,173.16420569164558</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-34.813620591523865,173.16449860555636</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-34.81428946077665,173.16487612675826</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
